--- a/output/pdf_financials_xlsx/ABRA.xlsx
+++ b/output/pdf_financials_xlsx/ABRA.xlsx
@@ -1327,25 +1327,25 @@
         <v>7.733181</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.541228</v>
+        <v>-1.541228</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>18.840655</v>
+        <v>-18.840655</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>20.904232</v>
+        <v>-20.904232</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>57.638217</v>
+        <v>-57.638217</v>
       </c>
     </row>
     <row r="17">
@@ -1627,25 +1627,25 @@
         <v>7.733181</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.541228</v>
+        <v>-1.541228</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>18.840655</v>
+        <v>-18.840655</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>20.904232</v>
+        <v>-20.904232</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>57.638217</v>
+        <v>-57.638217</v>
       </c>
     </row>
     <row r="21">
@@ -1801,25 +1801,25 @@
         <v>7.733181</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.541228</v>
+        <v>-1.541228</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.840655</v>
+        <v>-18.840655</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>20.904232</v>
+        <v>-20.904232</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>57.638217</v>
+        <v>-57.638217</v>
       </c>
     </row>
     <row r="24">
@@ -1987,22 +1987,22 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>55.342933</v>
+        <v>-55.342933</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>77.06140000000001</v>
+        <v>-77.06140000000001</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>471.016375</v>
+        <v>-471.016375</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>522.6058</v>
+        <v>-522.6058</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>110.549612</v>
+        <v>-110.549612</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>119.506214</v>
+        <v>-119.506214</v>
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
@@ -2047,25 +2047,25 @@
         <v>7.733181</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.541228</v>
+        <v>-1.541228</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.840655</v>
+        <v>-18.840655</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>20.904232</v>
+        <v>-20.904232</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>57.638217</v>
+        <v>-57.638217</v>
       </c>
     </row>
     <row r="28">
@@ -2163,25 +2163,25 @@
         <v>7.733181</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.541228</v>
+        <v>-1.541228</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.840655</v>
+        <v>-18.840655</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>20.904232</v>
+        <v>-20.904232</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>25.117199</v>
+        <v>-25.075411</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>57.714673</v>
+        <v>-57.561761</v>
       </c>
     </row>
     <row r="30">
@@ -2313,25 +2313,25 @@
         <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6116,25 +6116,25 @@
         <v>1.317252</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.317252</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.317252</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.357753</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.357753</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.357753</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.377442</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.057958</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>7.733181</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>57.638217</v>
+        <v>-57.638217</v>
       </c>
     </row>
     <row r="100">
@@ -15820,7 +15820,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -17719,7 +17723,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -35985,10 +35993,10 @@
         </is>
       </c>
       <c r="T269" s="5" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="U269" s="5" t="n">
-        <v>57.638217</v>
+        <v>-57.638217</v>
       </c>
     </row>
     <row r="270">
@@ -36484,10 +36492,10 @@
         </is>
       </c>
       <c r="T274" s="5" t="n">
-        <v>23.22137</v>
+        <v>-23.22137</v>
       </c>
       <c r="U274" s="5" t="n">
-        <v>58.867853</v>
+        <v>-58.867853</v>
       </c>
     </row>
     <row r="275">
@@ -37859,10 +37867,10 @@
         </is>
       </c>
       <c r="S288" s="5" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="T288" s="5" t="n">
-        <v>25.096305</v>
+        <v>-25.096305</v>
       </c>
       <c r="U288" t="inlineStr">
         <is>
@@ -38033,22 +38041,22 @@
         </is>
       </c>
       <c r="O290" s="5" t="n">
-        <v>4.537322</v>
+        <v>-4.537322</v>
       </c>
       <c r="P290" s="5" t="n">
-        <v>1.378133</v>
+        <v>-1.378133</v>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>14.084821</v>
+        <v>-14.084821</v>
       </c>
       <c r="R290" s="5" t="n">
-        <v>14.862353</v>
+        <v>-14.862353</v>
       </c>
       <c r="S290" s="5" t="n">
-        <v>19.649468</v>
+        <v>-19.649468</v>
       </c>
       <c r="T290" s="5" t="n">
-        <v>23.22137</v>
+        <v>-23.22137</v>
       </c>
       <c r="U290" t="inlineStr">
         <is>
@@ -38839,13 +38847,13 @@
         </is>
       </c>
       <c r="Q298" s="5" t="n">
-        <v>18.840655</v>
+        <v>-18.840655</v>
       </c>
       <c r="R298" s="5" t="n">
-        <v>20.904232</v>
+        <v>-20.904232</v>
       </c>
       <c r="S298" s="5" t="n">
-        <v>18.793434</v>
+        <v>-18.793434</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -41053,10 +41061,10 @@
         </is>
       </c>
       <c r="O320" s="5" t="n">
-        <v>3.320576</v>
+        <v>-3.320576</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>1.541228</v>
+        <v>-1.541228</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ABRA.xlsx
+++ b/output/pdf_financials_xlsx/ABRA.xlsx
@@ -943,22 +943,22 @@
         <v>0.0479</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.215985</v>
+        <v>0.294578</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.163459</v>
+        <v>0.227701</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.07829700000000001</v>
+        <v>0.131124</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.055855</v>
+        <v>0.09803099999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.047485</v>
+        <v>0.085102</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.046519</v>
+        <v>0.086822</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.434326</v>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.047485</v>
+        <v>-0.085102</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.046519</v>
+        <v>-0.086822</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.434326</v>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>7.7e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1098,22 +1098,22 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00722</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.298827</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.361797</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.557091</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-1.790496</v>
       </c>
     </row>
     <row r="13">
@@ -2023,7 +2023,7 @@
         <v>-0.357342</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.298375</v>
+        <v>-0.298452</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.242582</v>
@@ -2050,22 +2050,22 @@
         <v>-3.320576</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.541228</v>
+        <v>-1.534008</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-18.840655</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-20.904232</v>
+        <v>-20.605405</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-18.793434</v>
+        <v>-18.431637</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-25.096305</v>
+        <v>-24.539214</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-57.638217</v>
+        <v>-55.847721</v>
       </c>
     </row>
     <row r="28">
@@ -2139,7 +2139,7 @@
         <v>-0.357342</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.298375</v>
+        <v>-0.298452</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.242582</v>
@@ -2166,22 +2166,22 @@
         <v>-3.320576</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.541228</v>
+        <v>-1.534008</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-18.840655</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-20.904232</v>
+        <v>-20.605405</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-18.793434</v>
+        <v>-18.431637</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-25.075411</v>
+        <v>-24.51832</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-57.561761</v>
+        <v>-55.771265</v>
       </c>
     </row>
     <row r="30">
@@ -2439,10 +2439,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.299558</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -2450,28 +2448,28 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009875999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.086593</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000204</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.031417</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002379</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.295594</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022223</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.011662</v>
@@ -2563,10 +2561,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.299558</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -2574,28 +2570,28 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009875999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.086593</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000204</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.031417</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002379</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.295594</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.022223</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.011662</v>
@@ -3332,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.295594</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.040019</v>
+        <v>0.017796</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.005442</v>
@@ -15010,7 +15006,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -16830,7 +16826,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -19111,7 +19107,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -20547,7 +20543,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -35112,7 +35108,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -38278,7 +38274,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -45740,7 +45736,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -46225,7 +46221,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -47088,7 +47084,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -48298,7 +48294,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">

--- a/output/pdf_financials_xlsx/ABRA.xlsx
+++ b/output/pdf_financials_xlsx/ABRA.xlsx
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.002873</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>-3.320576</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.534008</v>
+        <v>-1.531135</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-18.840655</v>
@@ -39779,7 +39779,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ABRA.xlsx
+++ b/output/pdf_financials_xlsx/ABRA.xlsx
@@ -787,7 +787,7 @@
         <v>0.046519</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.35265</v>
+        <v>0.434326</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>1.514188</v>
@@ -799,19 +799,19 @@
         <v>0.481387</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.076408</v>
+        <v>2.801232</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>2.832471</v>
+        <v>3.594612</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>3.068913</v>
+        <v>3.873891</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.177568</v>
+        <v>2.360225</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>2.920354</v>
+        <v>5.009727</v>
       </c>
     </row>
     <row r="8">
@@ -973,19 +973,19 @@
         <v>0.531488</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.076408</v>
+        <v>2.801232</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2.832471</v>
+        <v>3.594612</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>3.068913</v>
+        <v>3.873891</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1.177568</v>
+        <v>2.360225</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>2.920354</v>
+        <v>5.009727</v>
       </c>
     </row>
     <row r="11">
@@ -1043,19 +1043,19 @@
         <v>-0.531488</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-2.076408</v>
+        <v>-2.801232</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-2.832471</v>
+        <v>-3.594612</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-3.068913</v>
+        <v>-3.873891</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-1.177568</v>
+        <v>-2.360225</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-2.920354</v>
+        <v>-5.009727</v>
       </c>
     </row>
     <row r="12">
@@ -1642,10 +1642,10 @@
         <v>-18.793434</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-25.096305</v>
+        <v>-25.07689</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-57.638217</v>
+        <v>-57.625847</v>
       </c>
     </row>
     <row r="21">
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-0.019415</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>-0.01237</v>
       </c>
     </row>
     <row r="22">
@@ -4362,19 +4362,19 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.212943</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.123245</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.153155</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.192028</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.004915</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
@@ -4747,13 +4747,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.03397</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.025667</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.012528</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0</v>
@@ -4807,13 +4807,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.03397</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.025667</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.012528</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -5058,10 +5058,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.025667</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.012528</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
@@ -5378,20 +5378,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.00299763366075223</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.0008256699025965576</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.0003964601751988147</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -6499,7 +6493,7 @@
         <v>-0.094939</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-2.296288</v>
+        <v>0.509806</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>7.733181</v>
@@ -7518,10 +7512,10 @@
         </is>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-18.659951</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0</v>
+        <v>-35.311831</v>
       </c>
     </row>
     <row r="115">
@@ -7584,10 +7578,10 @@
         </is>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>22.562551</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>36.011289</v>
       </c>
     </row>
     <row r="116">
@@ -11750,7 +11744,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -13071,7 +13069,11 @@
           <t>Lease liabilities 12,528</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -14598,7 +14600,11 @@
           <t>Lease liabilities (note 11)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -23983,7 +23989,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -24284,7 +24294,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -29827,7 +29841,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -34316,7 +34334,11 @@
           <t>Salaries, benefits and director fees (note 14)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -35710,7 +35732,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -35787,10 +35813,10 @@
         </is>
       </c>
       <c r="T267" s="5" t="n">
-        <v>25.07689</v>
+        <v>-25.07689</v>
       </c>
       <c r="U267" s="5" t="n">
-        <v>57.625847</v>
+        <v>-57.625847</v>
       </c>
     </row>
     <row r="268">
@@ -35809,7 +35835,11 @@
           <t>Loss from discontinued operation (note 9)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -35886,10 +35916,10 @@
         </is>
       </c>
       <c r="T268" s="5" t="n">
-        <v>0.019415</v>
+        <v>-0.019415</v>
       </c>
       <c r="U268" s="5" t="n">
-        <v>0.01237</v>
+        <v>-0.01237</v>
       </c>
     </row>
     <row r="269">
@@ -37106,7 +37136,11 @@
           <t>Salaries, benefits and director fees (note 13)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -44047,7 +44081,11 @@
           <t>Directors’ fees (note 10)</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
